--- a/New folder/For_printing_tag_Upgraded/DB_files/Spacing_position_DB.xlsx
+++ b/New folder/For_printing_tag_Upgraded/DB_files/Spacing_position_DB.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Field_name</t>
   </si>
@@ -64,13 +64,73 @@
   </si>
   <si>
     <t>Value</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Clarity</t>
+  </si>
+  <si>
+    <t>draw_party_logo</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>Prefix</t>
+  </si>
+  <si>
+    <t>Suffix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ART: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Batch No: </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MTR</t>
+  </si>
+  <si>
+    <t>date_name</t>
+  </si>
+  <si>
+    <t>Off_set_x_must_be_0</t>
+  </si>
+  <si>
+    <t>Column_purpose</t>
+  </si>
+  <si>
+    <t>Only when y cordinate is necessary</t>
+  </si>
+  <si>
+    <t>When cordinate is not necessary</t>
+  </si>
+  <si>
+    <t>Only when x cordinate is necessary (Does not work as text is placed at center always)</t>
+  </si>
+  <si>
+    <t>Only related to "x_position" as it is disabled. This value must be zero except overlapping cases.</t>
+  </si>
+  <si>
+    <t>Row purpose</t>
+  </si>
+  <si>
+    <t>It increases print quality</t>
+  </si>
+  <si>
+    <t>Length of single page</t>
+  </si>
+  <si>
+    <t>Width of single page</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,15 +149,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.8000000000000007"/>
+      <sz val="11"/>
       <name val="JetBrains Mono"/>
-      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="JetBrains Mono"/>
     </font>
     <font>
       <sz val="9.8000000000000007"/>
       <color theme="1"/>
       <name val="JetBrains Mono"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -120,17 +183,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -412,145 +480,311 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2">
-        <v>45</v>
-      </c>
-      <c r="C2">
-        <v>70</v>
+      <c r="F1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="D2">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4">
+        <v>45</v>
+      </c>
+      <c r="C3" s="4">
+        <v>70</v>
+      </c>
+      <c r="D3" s="4">
+        <v>15</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B4" s="4">
         <v>40</v>
       </c>
-      <c r="C3">
+      <c r="C4" s="4">
         <v>58</v>
       </c>
-      <c r="D3">
+      <c r="D4" s="4">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
+      <c r="E4" s="4"/>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
+      <c r="B5" s="4">
         <v>42</v>
       </c>
-      <c r="C4">
-        <v>48</v>
-      </c>
-      <c r="D4">
+      <c r="C5" s="4">
+        <v>35</v>
+      </c>
+      <c r="D5" s="4">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1201</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5">
+      <c r="B6" s="4">
         <v>2</v>
       </c>
-      <c r="C5">
+      <c r="C6" s="4">
+        <v>20</v>
+      </c>
+      <c r="D6" s="4">
+        <v>10</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>30214</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="4">
         <v>30</v>
       </c>
-      <c r="D5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
+      <c r="C7" s="4">
+        <v>10</v>
+      </c>
+      <c r="D7" s="4">
         <v>8</v>
       </c>
-      <c r="B6">
+      <c r="E7" s="4"/>
+      <c r="F7" s="4">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="4">
+        <v>45</v>
+      </c>
+      <c r="C8" s="4">
+        <v>12</v>
+      </c>
+      <c r="D8" s="4">
+        <v>6</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="4">
+        <v>45</v>
+      </c>
+      <c r="C9" s="4">
+        <v>3</v>
+      </c>
+      <c r="D9" s="4">
+        <v>8</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4">
+        <v>4</v>
+      </c>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4">
+        <v>66.44</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="K12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4">
+        <v>44.96</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="K13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4">
+        <v>20</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="K14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="7" customFormat="1" ht="73.5" customHeight="1">
+      <c r="A15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>30</v>
-      </c>
-      <c r="C6">
-        <v>20</v>
-      </c>
-      <c r="D6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>45</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10">
-        <v>132.44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11">
-        <v>84.96</v>
       </c>
     </row>
   </sheetData>
